--- a/backend/templates/blendedlab.xlsx
+++ b/backend/templates/blendedlab.xlsx
@@ -884,7 +884,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7571880" y="1567080"/>
-          <a:ext cx="702000" cy="519480"/>
+          <a:ext cx="500138" cy="519480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -927,7 +927,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="7571880" y="1567080"/>
-          <a:ext cx="702000" cy="519480"/>
+          <a:ext cx="500138" cy="519480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
